--- a/output/pdf_financials_xlsx/PA.xlsx
+++ b/output/pdf_financials_xlsx/PA.xlsx
@@ -1075,22 +1075,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.215405</v>
+        <v>-0.215405</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.684316</v>
+        <v>-0.684316</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.013454</v>
+        <v>-1.013454</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.695408</v>
+        <v>-1.695408</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.921476</v>
+        <v>-2.921476</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.597942</v>
+        <v>-1.597942</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3.064101</v>
+        <v>-3.064101</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-2.392547</v>
@@ -1299,22 +1299,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.215405</v>
+        <v>-0.215405</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.684316</v>
+        <v>-0.684316</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.013454</v>
+        <v>-1.013454</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.695408</v>
+        <v>-1.695408</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.921476</v>
+        <v>-2.921476</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.597942</v>
+        <v>-1.597942</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3.064101</v>
+        <v>-3.064101</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-2.392547</v>
@@ -1434,22 +1434,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.215405</v>
+        <v>-0.215405</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.684316</v>
+        <v>-0.684316</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.013454</v>
+        <v>-1.013454</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.695408</v>
+        <v>-1.695408</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.921476</v>
+        <v>-2.921476</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.597942</v>
+        <v>-1.597942</v>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>3.064101</v>
+        <v>-3.064101</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-2.392547</v>
@@ -1582,16 +1582,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>13.68632</v>
+        <v>-13.68632</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>16.8909</v>
+        <v>-16.8909</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>24.220114</v>
+        <v>-24.220114</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>29.21476</v>
+        <v>-29.21476</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>61.28202</v>
+        <v>-61.28202</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>65.284836</v>
@@ -1626,22 +1626,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.215405</v>
+        <v>-0.215405</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.684316</v>
+        <v>-0.684316</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.013454</v>
+        <v>-1.013454</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.695408</v>
+        <v>-1.695408</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.921476</v>
+        <v>-2.921476</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.597942</v>
+        <v>-1.597942</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.064101</v>
+        <v>-3.064101</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-2.392547</v>
@@ -1716,22 +1716,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.215405</v>
+        <v>-0.215405</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.684316</v>
+        <v>-0.684316</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.013454</v>
+        <v>-1.013454</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.70281</v>
+        <v>-1.688006</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.934629</v>
+        <v>-2.908323</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.611312</v>
+        <v>-1.584572</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>3.064101</v>
+        <v>-3.064101</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-2.392547</v>
@@ -1828,22 +1828,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -4647,10 +4647,10 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.416775</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
@@ -13140,7 +13140,11 @@
           <t>Reserve for warrants (Note 13)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -13662,7 +13666,11 @@
           <t>Reserve for warrants (Note 13)</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -27597,10 +27605,10 @@
         </is>
       </c>
       <c r="L282" s="5" t="n">
-        <v>3.064101</v>
+        <v>-3.064101</v>
       </c>
       <c r="M282" s="5" t="n">
-        <v>2.392547</v>
+        <v>-2.392547</v>
       </c>
       <c r="N282" t="inlineStr">
         <is>
@@ -27749,10 +27757,10 @@
         </is>
       </c>
       <c r="L284" s="5" t="n">
-        <v>3.068525</v>
+        <v>-3.068525</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>2.40006</v>
+        <v>-2.40006</v>
       </c>
       <c r="N284" t="inlineStr">
         <is>
@@ -29608,10 +29616,10 @@
         </is>
       </c>
       <c r="I309" s="5" t="n">
-        <v>2.921476</v>
+        <v>-2.921476</v>
       </c>
       <c r="J309" s="5" t="n">
-        <v>1.597942</v>
+        <v>-1.597942</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
@@ -30250,19 +30258,19 @@
         </is>
       </c>
       <c r="E318" s="5" t="n">
-        <v>0.215405</v>
+        <v>-0.215405</v>
       </c>
       <c r="F318" s="5" t="n">
-        <v>0.684316</v>
+        <v>-0.684316</v>
       </c>
       <c r="G318" s="5" t="n">
-        <v>1.013454</v>
+        <v>-1.013454</v>
       </c>
       <c r="H318" s="5" t="n">
-        <v>1.695408</v>
+        <v>-1.695408</v>
       </c>
       <c r="I318" s="5" t="n">
-        <v>2.921476</v>
+        <v>-2.921476</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PA.xlsx
+++ b/output/pdf_financials_xlsx/PA.xlsx
@@ -805,22 +805,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.050832</v>
+        <v>0.215405</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.274794</v>
+        <v>0.69229</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.470698</v>
+        <v>1.020694</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.492986</v>
+        <v>1.701003</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.568364</v>
+        <v>2.929948</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.566683</v>
+        <v>2.080643</v>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.157821</v>
+        <v>2.888493</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.195042</v>
+        <v>2.267246</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.148025</v>
+        <v>1.709294</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.184857</v>
+        <v>3.163328</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.149862</v>
+        <v>2.032791</v>
       </c>
     </row>
     <row r="11">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.050832</v>
+        <v>-0.215405</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.274794</v>
+        <v>-0.69229</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.470698</v>
+        <v>-1.020694</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.492986</v>
+        <v>-1.701003</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.568364</v>
+        <v>-2.929948</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.566683</v>
+        <v>-2.080643</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.157821</v>
+        <v>-2.888493</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.195042</v>
+        <v>-2.267246</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.148025</v>
+        <v>-1.709294</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.184857</v>
+        <v>-3.163328</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.149862</v>
+        <v>-2.032791</v>
       </c>
     </row>
     <row r="12">
@@ -898,19 +898,19 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007974</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00724</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005595</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008472</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002701</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -918,19 +918,19 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0063</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.006417</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001301</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.062194</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000203</v>
       </c>
     </row>
     <row r="13">
@@ -1629,19 +1629,19 @@
         <v>-0.215405</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.684316</v>
+        <v>-0.676342</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.013454</v>
+        <v>-1.006214</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.695408</v>
+        <v>-1.689813</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.921476</v>
+        <v>-2.913004</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.597942</v>
+        <v>-1.595241</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.064101</v>
+        <v>-3.057801</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.392547</v>
+        <v>-2.398964</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.272742</v>
+        <v>2.271441</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.220091</v>
+        <v>-3.282285</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.85383</v>
+        <v>-1.854033</v>
       </c>
     </row>
     <row r="28">
@@ -1719,19 +1719,19 @@
         <v>-0.215405</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.684316</v>
+        <v>-0.676342</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.013454</v>
+        <v>-1.006214</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.688006</v>
+        <v>-1.682411</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.908323</v>
+        <v>-2.899851</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.584572</v>
+        <v>-1.581871</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.064101</v>
+        <v>-3.057801</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.392547</v>
+        <v>-2.398964</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.272742</v>
+        <v>2.271441</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.220091</v>
+        <v>-3.282285</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.85383</v>
+        <v>-1.854033</v>
       </c>
     </row>
     <row r="30">
@@ -1976,13 +1976,13 @@
         <v>0.081302</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.040172</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.08791300000000001</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.140283</v>
       </c>
     </row>
     <row r="35">
@@ -2066,13 +2066,13 @@
         <v>0.081302</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.040172</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.08791300000000001</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.140283</v>
       </c>
     </row>
     <row r="37">
@@ -2606,13 +2606,13 @@
         <v>0.16581</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.241136</v>
+        <v>0.200964</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.22586</v>
+        <v>0.137947</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.213702</v>
+        <v>0.073419</v>
       </c>
     </row>
     <row r="49">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E216" s="5" t="n">
@@ -22614,16 +22614,16 @@
         <v>2.888493</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>-2.267246</v>
+        <v>2.267246</v>
       </c>
       <c r="N216" s="5" t="n">
-        <v>-1.709294</v>
+        <v>1.709294</v>
       </c>
       <c r="O216" s="5" t="n">
-        <v>-3.163328</v>
+        <v>3.163328</v>
       </c>
       <c r="P216" s="5" t="n">
-        <v>-2.032791</v>
+        <v>2.032791</v>
       </c>
     </row>
     <row r="217">
@@ -22870,7 +22870,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -27344,7 +27344,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -30180,7 +30180,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">

--- a/output/pdf_financials_xlsx/PA.xlsx
+++ b/output/pdf_financials_xlsx/PA.xlsx
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.157821</v>
+        <v>0.425108</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.195042</v>
+        <v>0.499977</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.148025</v>
+        <v>0.636414</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.184857</v>
+        <v>0.465842</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.149862</v>
+        <v>0.409051</v>
       </c>
     </row>
     <row r="8">
@@ -1694,19 +1694,19 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.00462</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.008168</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.008005</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.015813</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.018373</v>
       </c>
     </row>
     <row r="29">
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.057801</v>
+        <v>-3.053181</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.398964</v>
+        <v>-2.390796</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.271441</v>
+        <v>2.279446</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.282285</v>
+        <v>-3.266472</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.854033</v>
+        <v>-1.83566</v>
       </c>
     </row>
     <row r="30">
@@ -2282,10 +2282,10 @@
         <v>0.027899</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.008085</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>0.0608</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>0.009561999999999999</v>
@@ -2597,10 +2597,10 @@
         <v>0.020148</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.009585</v>
+        <v>0.0015</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.299227</v>
+        <v>0.238427</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.16581</v>
@@ -2822,22 +2822,22 @@
         <v>0.033484</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0</v>
+        <v>0.008026999999999999</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0</v>
+        <v>0.026457</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0</v>
+        <v>0.038304</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0</v>
+        <v>0.029769</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0</v>
+        <v>0.078072</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>0</v>
+        <v>0.056185</v>
       </c>
     </row>
     <row r="54">
@@ -4473,22 +4473,22 @@
         <v>5.657366</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>6.480295</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>9.457488</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>9.457488</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>10.012858</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0</v>
+        <v>10.065358</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0</v>
+        <v>11.972701</v>
       </c>
     </row>
     <row r="89">
@@ -4653,22 +4653,22 @@
         <v>1.416775</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.774775</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.215</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.947</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.17069</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.17069</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.725676</v>
       </c>
     </row>
     <row r="93">
@@ -6264,19 +6264,19 @@
         </is>
       </c>
       <c r="I128" s="3" t="n">
-        <v>0</v>
+        <v>-0.075807</v>
       </c>
       <c r="J128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K128" s="3" t="n">
-        <v>0</v>
+        <v>-0.02394</v>
       </c>
       <c r="L128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M128" s="3" t="n">
-        <v>0</v>
+        <v>-0.066981</v>
       </c>
     </row>
     <row r="129">
@@ -6944,7 +6944,11 @@
           <t>Prepaid expenses and other assets Note 6</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OtherAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -7084,7 +7088,11 @@
           <t>Equipment Note 7</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -7442,7 +7450,11 @@
           <t>Share capital Note 9</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -7582,7 +7594,11 @@
           <t>Warrant reserve Note 11</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -8002,7 +8018,11 @@
           <t>Share capital Note 9</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -8150,7 +8170,11 @@
           <t>Warrant reserve Note 11</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11752,7 +11776,11 @@
           <t>Receivables Note 8</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -11824,7 +11852,11 @@
           <t>Prepaid expenses Note 9</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -11896,7 +11928,11 @@
           <t>Equipment Note 10</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -12116,7 +12152,11 @@
           <t>Share capital Note 13</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -12260,7 +12300,11 @@
           <t>Warrant reserve Note 15</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -15158,7 +15202,11 @@
           <t>Depreciation Note 7</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -16244,7 +16292,11 @@
           <t>Share issue costs Note 9</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -18126,7 +18178,11 @@
           <t>Depreciation Note 10</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -18808,7 +18864,11 @@
           <t>Share issuance costs Note 13</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -22124,7 +22184,11 @@
           <t>Salaries, director and management fees Note 12</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -22442,7 +22506,11 @@
           <t>Depreciation Note 7</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -27112,7 +27180,11 @@
           <t>Depreciation Note 10</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PA.xlsx
+++ b/output/pdf_financials_xlsx/PA.xlsx
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.001199</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0.007402</v>
@@ -1722,7 +1722,7 @@
         <v>-0.676342</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.006214</v>
+        <v>-1.005015</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.682411</v>
@@ -3478,16 +3478,16 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.157203</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.381177</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.06571</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.096874</v>
       </c>
     </row>
     <row r="68">
@@ -5456,16 +5456,16 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005757</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.050759</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009977</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001149</v>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
@@ -5473,16 +5473,16 @@
         </is>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.02287</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.018081</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.060191</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
@@ -6247,7 +6247,7 @@
         <v>0</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0</v>
+        <v>-0.022644</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>0</v>
@@ -6525,16 +6525,16 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005757</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.050759</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009977</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001149</v>
       </c>
       <c r="H134" s="1" t="inlineStr">
         <is>
@@ -6542,16 +6542,16 @@
         </is>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.02287</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.018081</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.060191</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
@@ -6570,16 +6570,16 @@
         <v>-0.507321</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.986224</v>
+        <v>-0.991981</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.402357</v>
+        <v>-1.453116</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-2.367661</v>
+        <v>-2.377638</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-1.759046</v>
+        <v>-1.760195</v>
       </c>
       <c r="H135" s="1" t="inlineStr">
         <is>
@@ -6587,16 +6587,16 @@
         </is>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-2.597577</v>
+        <v>-2.620447</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-2.040926</v>
+        <v>-2.059007</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-1.270915</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-2.892068</v>
+        <v>-2.952259</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-1.869881</v>
@@ -6613,7 +6613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P332"/>
+  <dimension ref="A1:P335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16070,7 +16070,11 @@
           <t>Purchase of equipment Note 7</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -16218,7 +16222,11 @@
           <t>Proceeds from private placement Note 9</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -18562,7 +18570,11 @@
           <t>Purchase of equipment Note 10</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -18788,7 +18800,11 @@
           <t>Proceeds from private placement Note 13</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -19635,10 +19651,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G175" s="5" t="n">
+        <v>0.001199</v>
       </c>
       <c r="H175" s="5" t="n">
         <v>0.007402</v>
@@ -20221,10 +20235,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G183" s="5" t="n">
+        <v>-0.986224</v>
       </c>
       <c r="H183" s="5" t="n">
         <v>-1.402357</v>
@@ -20282,7 +20294,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -20367,10 +20383,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G185" s="5" t="n">
+        <v>-0.005757</v>
       </c>
       <c r="H185" s="5" t="n">
         <v>-0.050759</v>
@@ -20439,10 +20453,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G186" s="5" t="n">
+        <v>1.2</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -20595,10 +20607,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G188" s="5" t="n">
+        <v>-0.022644</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -20665,10 +20675,8 @@
       <c r="F189" s="5" t="n">
         <v>2.071867</v>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G189" s="5" t="n">
+        <v>1.177356</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -20821,10 +20829,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G191" s="5" t="n">
+        <v>1.564546</v>
       </c>
       <c r="H191" s="5" t="n">
         <v>1.749921</v>
@@ -20895,10 +20901,8 @@
       <c r="F192" s="5" t="n">
         <v>1.564546</v>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G192" s="5" t="n">
+        <v>1.749921</v>
       </c>
       <c r="H192" s="5" t="n">
         <v>0.296805</v>
@@ -21026,17 +21030,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>(Decrease) increase in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -21050,12 +21054,10 @@
         </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>0.001199</v>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.185375</v>
+      </c>
+      <c r="H194" s="5" t="n">
+        <v>-1.453116</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -21106,27 +21108,31 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>activities</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Cash used in operating activities</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E195" s="5" t="n">
-        <v>-0.181294</v>
-      </c>
-      <c r="F195" s="5" t="n">
-        <v>-0.507321</v>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>-0.986224</v>
+        <v>0.001199</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -21182,31 +21188,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Cash used in investing activities</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="n">
+        <v>-0.181294</v>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>-0.507321</v>
       </c>
       <c r="G196" s="5" t="n">
-        <v>-0.005757</v>
+        <v>-0.986224</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -21262,15 +21264,19 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Issuance of share capital</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>Cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -21282,7 +21288,7 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>1.2</v>
+        <v>-0.005757</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -21338,12 +21344,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Share issue costs                                                           (22,644)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Funds received pursuant to the Arrangement (Note 1)</t>
+          <t>Issuance of share capital</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -21352,13 +21358,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F198" s="5" t="n">
-        <v>1.943101</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>1.2</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -21419,7 +21425,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Increase in equity in net assets</t>
+          <t>Funds received pursuant to the Arrangement (Note 1)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -21429,7 +21435,7 @@
         </is>
       </c>
       <c r="F199" s="5" t="n">
-        <v>0.128766</v>
+        <v>1.943101</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -21495,7 +21501,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Cash provided from financing activities</t>
+          <t>Increase in equity in net assets</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -21505,10 +21511,12 @@
         </is>
       </c>
       <c r="F200" s="5" t="n">
-        <v>2.071867</v>
-      </c>
-      <c r="G200" s="5" t="n">
-        <v>1.177356</v>
+        <v>0.128766</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -21569,24 +21577,20 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Increase in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Cash provided from financing activities</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F201" s="5" t="n">
-        <v>1.564546</v>
+        <v>2.071867</v>
       </c>
       <c r="G201" s="5" t="n">
-        <v>0.185375</v>
+        <v>1.177356</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -21647,12 +21651,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
+          <t>Increase in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -21660,13 +21664,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F202" s="5" t="n">
+        <v>1.564546</v>
       </c>
       <c r="G202" s="5" t="n">
-        <v>1.564546</v>
+        <v>0.185375</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -21727,12 +21729,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -21740,11 +21742,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F203" s="5" t="n">
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" s="5" t="n">
         <v>1.564546</v>
-      </c>
-      <c r="G203" s="5" t="n">
-        <v>1.749921</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -21800,27 +21804,29 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Share issue costs                                                           (22,644)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Value-added taxes receivable</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F204" s="5" t="n">
-        <v>-0.026511</v>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.564546</v>
+      </c>
+      <c r="G204" s="5" t="n">
+        <v>1.749921</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -21876,12 +21882,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Funds received pursuant to the Arrangement (Note 1)</t>
+          <t>Value-added taxes receivable</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -21891,7 +21897,7 @@
         </is>
       </c>
       <c r="F205" s="5" t="n">
-        <v>1.943101</v>
+        <v>-0.026511</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -21957,15 +21963,17 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Increase in equity in net assets</t>
+          <t>Funds received pursuant to the Arrangement (Note 1)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
-      <c r="E206" s="5" t="n">
-        <v>0.181294</v>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F206" s="5" t="n">
-        <v>0.128766</v>
+        <v>1.943101</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -22031,21 +22039,15 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Increase in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in equity in net assets</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" s="5" t="n">
+        <v>0.181294</v>
       </c>
       <c r="F207" s="5" t="n">
-        <v>1.564546</v>
+        <v>0.128766</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -22101,29 +22103,31 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures Note 13 $</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
+          <t>Increase in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F208" s="5" t="n">
+        <v>1.564546</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -22155,17 +22159,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M208" s="5" t="n">
-        <v>1.529059</v>
-      </c>
-      <c r="N208" s="5" t="n">
-        <v>0.847732</v>
-      </c>
-      <c r="O208" s="5" t="n">
-        <v>2.495768</v>
-      </c>
-      <c r="P208" s="5" t="n">
-        <v>1.504702</v>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -22181,14 +22193,10 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Salaries, director and management fees Note 12</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenditures Note 13 $</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -22224,20 +22232,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L209" s="5" t="n">
-        <v>0.267287</v>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M209" s="5" t="n">
-        <v>0.304935</v>
+        <v>1.529059</v>
       </c>
       <c r="N209" s="5" t="n">
-        <v>0.488389</v>
+        <v>0.847732</v>
       </c>
       <c r="O209" s="5" t="n">
-        <v>0.280985</v>
+        <v>2.495768</v>
       </c>
       <c r="P209" s="5" t="n">
-        <v>0.259189</v>
+        <v>1.504702</v>
       </c>
     </row>
     <row r="210">
@@ -22253,7 +22263,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>Salaries, director and management fees Note 12</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -22266,20 +22276,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F210" s="5" t="n">
-        <v>0.030551</v>
-      </c>
-      <c r="G210" s="5" t="n">
-        <v>0.070009</v>
-      </c>
-      <c r="H210" s="5" t="n">
-        <v>0.055007</v>
-      </c>
-      <c r="I210" s="5" t="n">
-        <v>0.172386</v>
-      </c>
-      <c r="J210" s="5" t="n">
-        <v>0.198255</v>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -22287,19 +22307,19 @@
         </is>
       </c>
       <c r="L210" s="5" t="n">
-        <v>0.115148</v>
+        <v>0.267287</v>
       </c>
       <c r="M210" s="5" t="n">
-        <v>0.137282</v>
+        <v>0.304935</v>
       </c>
       <c r="N210" s="5" t="n">
-        <v>0.087718</v>
+        <v>0.488389</v>
       </c>
       <c r="O210" s="5" t="n">
-        <v>0.110023</v>
+        <v>0.280985</v>
       </c>
       <c r="P210" s="5" t="n">
-        <v>0.079198</v>
+        <v>0.259189</v>
       </c>
     </row>
     <row r="211">
@@ -22315,39 +22335,33 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Shareholder costs and filing fees</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F211" s="5" t="n">
+        <v>0.030551</v>
+      </c>
+      <c r="G211" s="5" t="n">
+        <v>0.070009</v>
+      </c>
+      <c r="H211" s="5" t="n">
+        <v>0.055007</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>0.172386</v>
+      </c>
+      <c r="J211" s="5" t="n">
+        <v>0.198255</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -22355,19 +22369,19 @@
         </is>
       </c>
       <c r="L211" s="5" t="n">
-        <v>0.079239</v>
+        <v>0.115148</v>
       </c>
       <c r="M211" s="5" t="n">
-        <v>0.040774</v>
+        <v>0.137282</v>
       </c>
       <c r="N211" s="5" t="n">
-        <v>0.05243</v>
+        <v>0.087718</v>
       </c>
       <c r="O211" s="5" t="n">
-        <v>0.060958</v>
+        <v>0.110023</v>
       </c>
       <c r="P211" s="5" t="n">
-        <v>0.060072</v>
+        <v>0.079198</v>
       </c>
     </row>
     <row r="212">
@@ -22383,31 +22397,39 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E212" s="5" t="n">
-        <v>0.004742</v>
-      </c>
-      <c r="F212" s="5" t="n">
-        <v>0.115967</v>
-      </c>
-      <c r="G212" s="5" t="n">
-        <v>0.065389</v>
-      </c>
-      <c r="H212" s="5" t="n">
-        <v>0.033171</v>
-      </c>
-      <c r="I212" s="5" t="n">
-        <v>0.03205</v>
-      </c>
-      <c r="J212" s="5" t="n">
-        <v>0.061754</v>
+          <t>Shareholder costs and filing fees</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
@@ -22415,19 +22437,19 @@
         </is>
       </c>
       <c r="L212" s="5" t="n">
-        <v>0.080604</v>
+        <v>0.079239</v>
       </c>
       <c r="M212" s="5" t="n">
-        <v>0.069882</v>
+        <v>0.040774</v>
       </c>
       <c r="N212" s="5" t="n">
-        <v>0.055246</v>
+        <v>0.05243</v>
       </c>
       <c r="O212" s="5" t="n">
-        <v>0.067686</v>
+        <v>0.060958</v>
       </c>
       <c r="P212" s="5" t="n">
-        <v>0.054598</v>
+        <v>0.060072</v>
       </c>
     </row>
     <row r="213">
@@ -22443,31 +22465,31 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Office and general</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E213" s="5" t="n">
-        <v>0.003146</v>
+        <v>0.004742</v>
       </c>
       <c r="F213" s="5" t="n">
-        <v>0.009566</v>
+        <v>0.115967</v>
       </c>
       <c r="G213" s="5" t="n">
-        <v>0.023069</v>
+        <v>0.065389</v>
       </c>
       <c r="H213" s="5" t="n">
-        <v>0.063985</v>
+        <v>0.033171</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>0.025611</v>
+        <v>0.03205</v>
       </c>
       <c r="J213" s="5" t="n">
-        <v>0.029143</v>
+        <v>0.061754</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
@@ -22475,19 +22497,19 @@
         </is>
       </c>
       <c r="L213" s="5" t="n">
-        <v>0.040082</v>
+        <v>0.080604</v>
       </c>
       <c r="M213" s="5" t="n">
-        <v>0.055571</v>
+        <v>0.069882</v>
       </c>
       <c r="N213" s="5" t="n">
-        <v>0.057478</v>
+        <v>0.055246</v>
       </c>
       <c r="O213" s="5" t="n">
-        <v>0.07298300000000001</v>
+        <v>0.067686</v>
       </c>
       <c r="P213" s="5" t="n">
-        <v>0.067831</v>
+        <v>0.054598</v>
       </c>
     </row>
     <row r="214">
@@ -22503,65 +22525,51 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Depreciation Note 7</t>
+          <t>Office and general</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="n">
+        <v>0.003146</v>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>0.009566</v>
+      </c>
+      <c r="G214" s="5" t="n">
+        <v>0.023069</v>
+      </c>
+      <c r="H214" s="5" t="n">
+        <v>0.063985</v>
+      </c>
+      <c r="I214" s="5" t="n">
+        <v>0.025611</v>
+      </c>
+      <c r="J214" s="5" t="n">
+        <v>0.029143</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L214" s="5" t="n">
+        <v>0.040082</v>
       </c>
       <c r="M214" s="5" t="n">
-        <v>0.008168</v>
+        <v>0.055571</v>
       </c>
       <c r="N214" s="5" t="n">
-        <v>0.008005</v>
+        <v>0.057478</v>
       </c>
       <c r="O214" s="5" t="n">
-        <v>0.015813</v>
+        <v>0.07298300000000001</v>
       </c>
       <c r="P214" s="5" t="n">
-        <v>0.018373</v>
+        <v>0.067831</v>
       </c>
     </row>
     <row r="215">
@@ -22577,10 +22585,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Share-based compensation Notes 10,12</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
+          <t>Depreciation Note 7</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -22622,16 +22634,16 @@
         </is>
       </c>
       <c r="M215" s="5" t="n">
-        <v>0.121575</v>
+        <v>0.008168</v>
       </c>
       <c r="N215" s="5" t="n">
-        <v>0.112296</v>
+        <v>0.008005</v>
       </c>
       <c r="O215" s="5" t="n">
-        <v>0.059112</v>
+        <v>0.015813</v>
       </c>
       <c r="P215" s="5" t="n">
-        <v>-0.011172</v>
+        <v>0.018373</v>
       </c>
     </row>
     <row r="216">
@@ -22647,51 +22659,61 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E216" s="5" t="n">
-        <v>0.215405</v>
-      </c>
-      <c r="F216" s="5" t="n">
-        <v>0.69229</v>
-      </c>
-      <c r="G216" s="5" t="n">
-        <v>1.020694</v>
-      </c>
-      <c r="H216" s="5" t="n">
-        <v>1.701003</v>
-      </c>
-      <c r="I216" s="5" t="n">
-        <v>2.929948</v>
-      </c>
-      <c r="J216" s="5" t="n">
-        <v>2.080643</v>
+          <t>Share-based compensation Notes 10,12</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L216" s="5" t="n">
-        <v>2.888493</v>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M216" s="5" t="n">
-        <v>2.267246</v>
+        <v>0.121575</v>
       </c>
       <c r="N216" s="5" t="n">
-        <v>1.709294</v>
+        <v>0.112296</v>
       </c>
       <c r="O216" s="5" t="n">
-        <v>3.163328</v>
+        <v>0.059112</v>
       </c>
       <c r="P216" s="5" t="n">
-        <v>2.032791</v>
+        <v>-0.011172</v>
       </c>
     </row>
     <row r="217">
@@ -22702,70 +22724,56 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="n">
+        <v>0.215405</v>
+      </c>
+      <c r="F217" s="5" t="n">
+        <v>0.69229</v>
+      </c>
+      <c r="G217" s="5" t="n">
+        <v>1.020694</v>
+      </c>
+      <c r="H217" s="5" t="n">
+        <v>1.701003</v>
+      </c>
+      <c r="I217" s="5" t="n">
+        <v>2.929948</v>
+      </c>
+      <c r="J217" s="5" t="n">
+        <v>2.080643</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L217" s="5" t="n">
+        <v>2.888493</v>
       </c>
       <c r="M217" s="5" t="n">
-        <v>0.002189</v>
+        <v>2.267246</v>
       </c>
       <c r="N217" s="5" t="n">
-        <v>0.002829</v>
+        <v>1.709294</v>
       </c>
       <c r="O217" s="5" t="n">
-        <v>0.001851</v>
+        <v>3.163328</v>
       </c>
       <c r="P217" s="5" t="n">
-        <v>0.002833</v>
+        <v>2.032791</v>
       </c>
     </row>
     <row r="218">
@@ -22781,12 +22789,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Gain (loss) on foreign exchange</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -22829,21 +22837,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M218" s="5" t="n">
+        <v>0.002189</v>
+      </c>
+      <c r="N218" s="5" t="n">
+        <v>0.002829</v>
       </c>
       <c r="O218" s="5" t="n">
-        <v>-0.01565</v>
+        <v>0.001851</v>
       </c>
       <c r="P218" s="5" t="n">
-        <v>0.0857</v>
+        <v>0.002833</v>
       </c>
     </row>
     <row r="219">
@@ -22859,10 +22863,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Gain on sale of investment in associate Note 16</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
+          <t>Gain (loss) on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -22908,16 +22916,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N219" s="5" t="n">
-        <v>0.065425</v>
-      </c>
-      <c r="O219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O219" s="5" t="n">
+        <v>-0.01565</v>
       </c>
       <c r="P219" s="5" t="n">
-        <v>0.177295</v>
+        <v>0.0857</v>
       </c>
     </row>
     <row r="220">
@@ -22933,14 +22941,10 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Gain on sale of investment in associate Note 16</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -22981,17 +22985,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M220" s="5" t="n">
-        <v>0.006417</v>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N220" s="5" t="n">
-        <v>0.001301</v>
-      </c>
-      <c r="O220" s="5" t="n">
-        <v>0.062194</v>
+        <v>0.065425</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P220" s="5" t="n">
-        <v>0.000203</v>
+        <v>0.177295</v>
       </c>
     </row>
     <row r="221">
@@ -23007,10 +23015,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Advance royalty Note 16</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -23051,23 +23063,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M221" s="5" t="n">
+        <v>0.006417</v>
+      </c>
+      <c r="N221" s="5" t="n">
+        <v>0.001301</v>
       </c>
       <c r="O221" s="5" t="n">
-        <v>0.13561</v>
-      </c>
-      <c r="P221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.062194</v>
+      </c>
+      <c r="P221" s="5" t="n">
+        <v>0.000203</v>
       </c>
     </row>
     <row r="222">
@@ -23083,7 +23089,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Share of loss of associate Note 16</t>
+          <t>Advance royalty Note 16</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -23138,10 +23144,12 @@
         </is>
       </c>
       <c r="O222" s="5" t="n">
-        <v>-0.237066</v>
-      </c>
-      <c r="P222" s="5" t="n">
-        <v>-0.081404</v>
+        <v>0.13561</v>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -23157,14 +23165,10 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share of loss of associate Note 16</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -23216,10 +23220,10 @@
         </is>
       </c>
       <c r="O223" s="5" t="n">
-        <v>-3.220091</v>
+        <v>-0.237066</v>
       </c>
       <c r="P223" s="5" t="n">
-        <v>-1.85383</v>
+        <v>-0.081404</v>
       </c>
     </row>
     <row r="224">
@@ -23230,15 +23234,19 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>not subsequently reclassify into loss</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Exchange difference on translation of foreign subsidiaries</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -23290,10 +23298,10 @@
         </is>
       </c>
       <c r="O224" s="5" t="n">
-        <v>0.03513</v>
+        <v>-3.220091</v>
       </c>
       <c r="P224" s="5" t="n">
-        <v>-0.013058</v>
+        <v>-1.85383</v>
       </c>
     </row>
     <row r="225">
@@ -23309,14 +23317,10 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Net comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Exchange difference on translation of foreign subsidiaries</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -23368,10 +23372,10 @@
         </is>
       </c>
       <c r="O225" s="5" t="n">
-        <v>-3.184961</v>
+        <v>0.03513</v>
       </c>
       <c r="P225" s="5" t="n">
-        <v>-1.866888</v>
+        <v>-0.013058</v>
       </c>
     </row>
     <row r="226">
@@ -23382,17 +23386,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Net Loss per share</t>
+          <t>not subsequently reclassify into loss</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Net comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -23430,11 +23434,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L226" s="5" t="n">
-        <v>5e-08</v>
-      </c>
-      <c r="M226" s="5" t="n">
-        <v>4e-08</v>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
@@ -23442,10 +23450,10 @@
         </is>
       </c>
       <c r="O226" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-3.184961</v>
       </c>
       <c r="P226" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-1.866888</v>
       </c>
     </row>
     <row r="227">
@@ -23461,7 +23469,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding - basic and diluted</t>
+          <t>Basic and diluted loss per share $</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -23505,10 +23513,10 @@
         </is>
       </c>
       <c r="L227" s="5" t="n">
-        <v>56.024562</v>
+        <v>5e-08</v>
       </c>
       <c r="M227" s="5" t="n">
-        <v>65.284836</v>
+        <v>4e-08</v>
       </c>
       <c r="N227" t="inlineStr">
         <is>
@@ -23516,10 +23524,10 @@
         </is>
       </c>
       <c r="O227" s="5" t="n">
-        <v>71.386202</v>
+        <v>-4e-08</v>
       </c>
       <c r="P227" s="5" t="n">
-        <v>73.98826099999999</v>
+        <v>-3e-08</v>
       </c>
     </row>
     <row r="228">
@@ -23530,15 +23538,19 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>shares      Amount    Stock Options      Warrants      Translation            Deficit           Total</t>
+          <t>Net Loss per share</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2023 71,284,836 $ 10,012,858 $ 945,480 $ 170,690 $ (54,848) $</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -23574,15 +23586,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L228" s="5" t="n">
+        <v>56.024562</v>
+      </c>
+      <c r="M228" s="5" t="n">
+        <v>65.284836</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -23590,10 +23598,10 @@
         </is>
       </c>
       <c r="O228" s="5" t="n">
-        <v>2.942993</v>
+        <v>71.386202</v>
       </c>
       <c r="P228" s="5" t="n">
-        <v>-8.131187000000001</v>
+        <v>73.98826099999999</v>
       </c>
     </row>
     <row r="229">
@@ -23609,7 +23617,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Shares issued for acquisition of mineral property 350,000 52,500 - - -</t>
+          <t>Balance at December 31, 2023 71,284,836 $ 10,012,858 $ 945,480 $ 170,690 $ (54,848) $</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -23664,12 +23672,10 @@
         </is>
       </c>
       <c r="O229" s="5" t="n">
-        <v>0.0525</v>
-      </c>
-      <c r="P229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.942993</v>
+      </c>
+      <c r="P229" s="5" t="n">
+        <v>-8.131187000000001</v>
       </c>
     </row>
     <row r="230">
@@ -23685,7 +23691,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Expiry of stock options - - (330,694) - -</t>
+          <t>Shares issued for acquisition of mineral property 350,000 52,500 - - -</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -23739,13 +23745,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P230" s="5" t="n">
-        <v>0.330694</v>
+      <c r="O230" s="5" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="231">
@@ -23761,7 +23767,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Cancellation of stock options - - (65,023) - -</t>
+          <t>Expiry of stock options - - (330,694) - -</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -23821,7 +23827,7 @@
         </is>
       </c>
       <c r="P231" s="5" t="n">
-        <v>0.065023</v>
+        <v>0.330694</v>
       </c>
     </row>
     <row r="232">
@@ -23837,7 +23843,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 59,112 - -</t>
+          <t>Cancellation of stock options - - (65,023) - -</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -23891,13 +23897,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O232" s="5" t="n">
-        <v>0.059112</v>
-      </c>
-      <c r="P232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P232" s="5" t="n">
+        <v>0.065023</v>
       </c>
     </row>
     <row r="233">
@@ -23913,14 +23919,10 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - -</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation - - 59,112 - -</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -23972,10 +23974,12 @@
         </is>
       </c>
       <c r="O233" s="5" t="n">
-        <v>-3.220091</v>
-      </c>
-      <c r="P233" s="5" t="n">
-        <v>-3.220091</v>
+        <v>0.059112</v>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="234">
@@ -23991,10 +23995,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Other comprehensive loss - - - - 35,130</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>Net loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -24046,12 +24054,10 @@
         </is>
       </c>
       <c r="O234" s="5" t="n">
-        <v>0.03513</v>
-      </c>
-      <c r="P234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.220091</v>
+      </c>
+      <c r="P234" s="5" t="n">
+        <v>-3.220091</v>
       </c>
     </row>
     <row r="235">
@@ -24067,7 +24073,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2024 71,634,836 10,065,358 608,875 170,690 (19,718)</t>
+          <t>Other comprehensive loss - - - - 35,130</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -24122,10 +24128,12 @@
         </is>
       </c>
       <c r="O235" s="5" t="n">
-        <v>-0.130356</v>
-      </c>
-      <c r="P235" s="5" t="n">
-        <v>-10.955561</v>
+        <v>0.03513</v>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="236">
@@ -24141,7 +24149,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Shares issued for cash as part of unit financing 21,600,000 2,700,000 - - -</t>
+          <t>Balance at December 31, 2024 71,634,836 10,065,358 608,875 170,690 (19,718)</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -24196,12 +24204,10 @@
         </is>
       </c>
       <c r="O236" s="5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.130356</v>
+      </c>
+      <c r="P236" s="5" t="n">
+        <v>-10.955561</v>
       </c>
     </row>
     <row r="237">
@@ -24217,7 +24223,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Warrants issued as part of unit financing - (727,800) - 727,800 -</t>
+          <t>Shares issued for cash as part of unit financing 21,600,000 2,700,000 - - -</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -24271,10 +24277,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O237" s="5" t="n">
+        <v>2.7</v>
       </c>
       <c r="P237" t="inlineStr">
         <is>
@@ -24295,7 +24299,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Share issue costs – cash - (56,546) - (10,435) -</t>
+          <t>Warrants issued as part of unit financing - (727,800) - 727,800 -</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -24349,8 +24353,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O238" s="5" t="n">
-        <v>-0.066981</v>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
@@ -24371,7 +24377,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Share issue costs – finder warrants - (8,311) - 8,311 -</t>
+          <t>Share issue costs – cash - (56,546) - (10,435) -</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -24425,10 +24431,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O239" s="5" t="n">
+        <v>-0.066981</v>
       </c>
       <c r="P239" t="inlineStr">
         <is>
@@ -24449,7 +24453,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Expiry of warrants - - - (170,690) -</t>
+          <t>Share issue costs – finder warrants - (8,311) - 8,311 -</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -24508,8 +24512,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P240" s="5" t="n">
-        <v>0.17069</v>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="241">
@@ -24525,7 +24531,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Share-based compensation - - (11,172) - -</t>
+          <t>Expiry of warrants - - - (170,690) -</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -24579,13 +24585,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O241" s="5" t="n">
-        <v>-0.011172</v>
-      </c>
-      <c r="P241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P241" s="5" t="n">
+        <v>0.17069</v>
       </c>
     </row>
     <row r="242">
@@ -24601,7 +24607,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Expiry of stock options - - (307,396) - -</t>
+          <t>Share-based compensation - - (11,172) - -</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -24655,13 +24661,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P242" s="5" t="n">
-        <v>0.307396</v>
+      <c r="O242" s="5" t="n">
+        <v>-0.011172</v>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="243">
@@ -24677,7 +24683,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Other comprehensive income - - - - (13,058)</t>
+          <t>Expiry of stock options - - (307,396) - -</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -24731,13 +24737,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O243" s="5" t="n">
-        <v>-0.013058</v>
-      </c>
-      <c r="P243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P243" s="5" t="n">
+        <v>0.307396</v>
       </c>
     </row>
     <row r="244">
@@ -24753,7 +24759,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2025 93,234,836 $ 11,972,701 $ 290,307 $ 725,676 $ (32,776) $</t>
+          <t>Other comprehensive income - - - - (13,058)</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -24808,10 +24814,12 @@
         </is>
       </c>
       <c r="O244" s="5" t="n">
-        <v>0.624603</v>
-      </c>
-      <c r="P244" s="5" t="n">
-        <v>-12.331305</v>
+        <v>-0.013058</v>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="245">
@@ -24822,12 +24830,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Toronto, Ontario</t>
+          <t>shares      Amount    Stock Options      Warrants      Translation            Deficit           Total</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>Balance at December 31, 2025 93,234,836 $ 11,972,701 $ 290,307 $ 725,676 $ (32,776) $</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -24876,16 +24884,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N245" s="5" t="n">
-        <v>0.002025</v>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O245" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="P245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.624603</v>
+      </c>
+      <c r="P245" s="5" t="n">
+        <v>-12.331305</v>
       </c>
     </row>
     <row r="246">
@@ -24896,12 +24904,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Toronto, Ontario</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Gain on dilution Note 16</t>
+          <t>April</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -24951,12 +24959,10 @@
         </is>
       </c>
       <c r="N246" s="5" t="n">
-        <v>0.241963</v>
-      </c>
-      <c r="O246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002025</v>
+      </c>
+      <c r="O246" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="P246" t="inlineStr">
         <is>
@@ -24977,14 +24983,10 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Loss on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Gain on dilution Note 16</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -25025,11 +25027,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M247" s="5" t="n">
-        <v>-0.007263</v>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N247" s="5" t="n">
-        <v>-0.007169</v>
+        <v>0.241963</v>
       </c>
       <c r="O247" t="inlineStr">
         <is>
@@ -25055,10 +25059,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Advance royalty Note 12, 16</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
+          <t>Loss on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -25100,10 +25108,10 @@
         </is>
       </c>
       <c r="M248" s="5" t="n">
-        <v>0.06468500000000001</v>
+        <v>-0.007263</v>
       </c>
       <c r="N248" s="5" t="n">
-        <v>0.067715</v>
+        <v>-0.007169</v>
       </c>
       <c r="O248" t="inlineStr">
         <is>
@@ -25129,7 +25137,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Share of income (loss) of associate Note 16</t>
+          <t>Advance royalty Note 12, 16</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -25174,10 +25182,10 @@
         </is>
       </c>
       <c r="M249" s="5" t="n">
-        <v>-0.186951</v>
+        <v>0.06468500000000001</v>
       </c>
       <c r="N249" s="5" t="n">
-        <v>3.61563</v>
+        <v>0.067715</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
@@ -25203,14 +25211,10 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Net income (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share of income (loss) of associate Note 16</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -25252,10 +25256,10 @@
         </is>
       </c>
       <c r="M250" s="5" t="n">
-        <v>-2.392547</v>
+        <v>-0.186951</v>
       </c>
       <c r="N250" s="5" t="n">
-        <v>2.272742</v>
+        <v>3.61563</v>
       </c>
       <c r="O250" t="inlineStr">
         <is>
@@ -25276,15 +25280,19 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>not subsequently reclassify into income</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Exchange loss on translation of foreign subsidiaries</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>Net income (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -25326,10 +25334,10 @@
         </is>
       </c>
       <c r="M251" s="5" t="n">
-        <v>-0.007513</v>
+        <v>-2.392547</v>
       </c>
       <c r="N251" s="5" t="n">
-        <v>-0.031628</v>
+        <v>2.272742</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
@@ -25350,12 +25358,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Net Income (loss) per share</t>
+          <t>not subsequently reclassify into income</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>- Basic $</t>
+          <t>Exchange loss on translation of foreign subsidiaries</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -25400,10 +25408,10 @@
         </is>
       </c>
       <c r="M252" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-0.007513</v>
       </c>
       <c r="N252" s="5" t="n">
-        <v>3e-08</v>
+        <v>-0.031628</v>
       </c>
       <c r="O252" t="inlineStr">
         <is>
@@ -25429,7 +25437,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>- Diluted $</t>
+          <t>- Basic $</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -25498,19 +25506,15 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Net Income (loss) per share</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>- Basic</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>- Diluted $</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -25552,10 +25556,10 @@
         </is>
       </c>
       <c r="M254" s="5" t="n">
-        <v>65.284836</v>
+        <v>-4e-08</v>
       </c>
       <c r="N254" s="5" t="n">
-        <v>68.572507</v>
+        <v>3e-08</v>
       </c>
       <c r="O254" t="inlineStr">
         <is>
@@ -25581,12 +25585,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>- Diluted</t>
+          <t>- Basic</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>DilutedAverageShares</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -25633,7 +25637,7 @@
         <v>65.284836</v>
       </c>
       <c r="N255" s="5" t="n">
-        <v>68.599868</v>
+        <v>68.572507</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
@@ -25654,15 +25658,19 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>shares      Amount    Stock Options       Warrants      Translation           Deficit           Total</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2021 65,284,836 $ 9,457,488 $ 1,178,044 $ 2,215,000 $ (15,707) $</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
+          <t>- Diluted</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -25704,10 +25712,10 @@
         </is>
       </c>
       <c r="M256" s="5" t="n">
-        <v>2.142008</v>
+        <v>65.284836</v>
       </c>
       <c r="N256" s="5" t="n">
-        <v>-10.692817</v>
+        <v>68.599868</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
@@ -25733,7 +25741,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Expiry of warrants - - - (268,000) -</t>
+          <t>Balance at December 31, 2021 65,284,836 $ 9,457,488 $ 1,178,044 $ 2,215,000 $ (15,707) $</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -25777,13 +25785,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M257" s="5" t="n">
+        <v>2.142008</v>
       </c>
       <c r="N257" s="5" t="n">
-        <v>0.268</v>
+        <v>-10.692817</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
@@ -25809,7 +25815,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Expiry of stock options - - (101,333) - -</t>
+          <t>Expiry of warrants - - - (268,000) -</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -25859,7 +25865,7 @@
         </is>
       </c>
       <c r="N258" s="5" t="n">
-        <v>0.101333</v>
+        <v>0.268</v>
       </c>
       <c r="O258" t="inlineStr">
         <is>
@@ -25885,7 +25891,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 121,575 - -</t>
+          <t>Expiry of stock options - - (101,333) - -</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -25929,13 +25935,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M259" s="5" t="n">
-        <v>0.121575</v>
-      </c>
-      <c r="N259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="5" t="n">
+        <v>0.101333</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -25961,14 +25967,10 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - -</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation - - 121,575 - -</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -26010,10 +26012,12 @@
         </is>
       </c>
       <c r="M260" s="5" t="n">
-        <v>-2.392547</v>
-      </c>
-      <c r="N260" s="5" t="n">
-        <v>-2.392547</v>
+        <v>0.121575</v>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
@@ -26039,10 +26043,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Other comprehensive loss - - - - (7,513)</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>Net loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -26084,12 +26092,10 @@
         </is>
       </c>
       <c r="M261" s="5" t="n">
-        <v>-0.007513</v>
-      </c>
-      <c r="N261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.392547</v>
+      </c>
+      <c r="N261" s="5" t="n">
+        <v>-2.392547</v>
       </c>
       <c r="O261" t="inlineStr">
         <is>
@@ -26115,7 +26121,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2022 65,284,836 9,457,488 1,198,286 1,947,000 (23,220)</t>
+          <t>Other comprehensive loss - - - - (7,513)</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -26160,10 +26166,12 @@
         </is>
       </c>
       <c r="M262" s="5" t="n">
-        <v>-0.136477</v>
-      </c>
-      <c r="N262" s="5" t="n">
-        <v>-12.716031</v>
+        <v>-0.007513</v>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
@@ -26189,7 +26197,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Shares issued for cash as part of unit financing 6,000,000 750,000 - - -</t>
+          <t>Balance at December 31, 2022 65,284,836 9,457,488 1,198,286 1,947,000 (23,220)</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -26234,12 +26242,10 @@
         </is>
       </c>
       <c r="M263" s="5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.136477</v>
+      </c>
+      <c r="N263" s="5" t="n">
+        <v>-12.716031</v>
       </c>
       <c r="O263" t="inlineStr">
         <is>
@@ -26265,7 +26271,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Warrants issued as part of unit financing - (175,200) - 175,200 -</t>
+          <t>Shares issued for cash as part of unit financing 6,000,000 750,000 - - -</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -26309,10 +26315,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M264" s="5" t="n">
+        <v>0.75</v>
       </c>
       <c r="N264" t="inlineStr">
         <is>
@@ -26343,7 +26347,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Share issue costs - cash - (18,340) - (5,600) -</t>
+          <t>Warrants issued as part of unit financing - (175,200) - 175,200 -</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -26387,8 +26391,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M265" s="5" t="n">
-        <v>-0.02394</v>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N265" t="inlineStr">
         <is>
@@ -26419,7 +26425,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Share issue costs – finder warrants - (1,090) - 1,090 -</t>
+          <t>Share issue costs - cash - (18,340) - (5,600) -</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -26463,10 +26469,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M266" s="5" t="n">
+        <v>-0.02394</v>
       </c>
       <c r="N266" t="inlineStr">
         <is>
@@ -26497,7 +26501,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Expiry of warrants - - - (1,947,000) -</t>
+          <t>Share issue costs – finder warrants - (1,090) - 1,090 -</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -26546,8 +26550,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N267" s="5" t="n">
-        <v>1.947</v>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
@@ -26573,7 +26579,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Expiry of stock options - - (278,132) - -</t>
+          <t>Expiry of warrants - - - (1,947,000) -</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -26623,7 +26629,7 @@
         </is>
       </c>
       <c r="N268" s="5" t="n">
-        <v>0.278132</v>
+        <v>1.947</v>
       </c>
       <c r="O268" t="inlineStr">
         <is>
@@ -26649,7 +26655,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Cancellation of stock options - - (86,970) - -</t>
+          <t>Expiry of stock options - - (278,132) - -</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -26699,7 +26705,7 @@
         </is>
       </c>
       <c r="N269" s="5" t="n">
-        <v>0.08697000000000001</v>
+        <v>0.278132</v>
       </c>
       <c r="O269" t="inlineStr">
         <is>
@@ -26725,7 +26731,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 112,296 - -</t>
+          <t>Cancellation of stock options - - (86,970) - -</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -26769,13 +26775,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M270" s="5" t="n">
-        <v>0.112296</v>
-      </c>
-      <c r="N270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" s="5" t="n">
+        <v>0.08697000000000001</v>
       </c>
       <c r="O270" t="inlineStr">
         <is>
@@ -26801,14 +26807,10 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Net income for the year - - - - -</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation - - 112,296 - -</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -26850,10 +26852,12 @@
         </is>
       </c>
       <c r="M271" s="5" t="n">
-        <v>2.272742</v>
-      </c>
-      <c r="N271" s="5" t="n">
-        <v>2.272742</v>
+        <v>0.112296</v>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O271" t="inlineStr">
         <is>
@@ -26879,10 +26883,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Other comprehensive loss - - - - (31,628)</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
+          <t>Net income for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -26924,12 +26932,10 @@
         </is>
       </c>
       <c r="M272" s="5" t="n">
-        <v>-0.031628</v>
-      </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.272742</v>
+      </c>
+      <c r="N272" s="5" t="n">
+        <v>2.272742</v>
       </c>
       <c r="O272" t="inlineStr">
         <is>
@@ -26955,7 +26961,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2023 71,284,836 $ 10,012,858 $ 945,480 $ 170,690 $ (54,848) $</t>
+          <t>Other comprehensive loss - - - - (31,628)</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -27000,10 +27006,12 @@
         </is>
       </c>
       <c r="M273" s="5" t="n">
-        <v>2.942993</v>
-      </c>
-      <c r="N273" s="5" t="n">
-        <v>-8.131187000000001</v>
+        <v>-0.031628</v>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O273" t="inlineStr">
         <is>
@@ -27024,12 +27032,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>shares      Amount    Stock Options       Warrants      Translation           Deficit           Total</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures Notes 12, 16 $</t>
+          <t>Balance at December 31, 2023 71,284,836 $ 10,012,858 $ 945,480 $ 170,690 $ (54,848) $</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -27068,16 +27076,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L274" s="5" t="n">
-        <v>1.801513</v>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M274" s="5" t="n">
-        <v>1.529059</v>
-      </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.942993</v>
+      </c>
+      <c r="N274" s="5" t="n">
+        <v>-8.131187000000001</v>
       </c>
       <c r="O274" t="inlineStr">
         <is>
@@ -27103,7 +27111,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Share-based compensation Notes 12, 14</t>
+          <t>Exploration and evaluation expenditures Notes 12, 16 $</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -27143,10 +27151,10 @@
         </is>
       </c>
       <c r="L275" s="5" t="n">
-        <v>0.5</v>
+        <v>1.801513</v>
       </c>
       <c r="M275" s="5" t="n">
-        <v>0.121575</v>
+        <v>1.529059</v>
       </c>
       <c r="N275" t="inlineStr">
         <is>
@@ -27177,14 +27185,10 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Depreciation Note 10</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Share-based compensation Notes 12, 14</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -27221,10 +27225,10 @@
         </is>
       </c>
       <c r="L276" s="5" t="n">
-        <v>0.00462</v>
+        <v>0.5</v>
       </c>
       <c r="M276" s="5" t="n">
-        <v>0.008168</v>
+        <v>0.121575</v>
       </c>
       <c r="N276" t="inlineStr">
         <is>
@@ -27250,17 +27254,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Other (income) expense</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Depreciation Note 10</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -27299,10 +27303,10 @@
         </is>
       </c>
       <c r="L277" s="5" t="n">
-        <v>0.002591</v>
+        <v>0.00462</v>
       </c>
       <c r="M277" s="5" t="n">
-        <v>0.002189</v>
+        <v>0.008168</v>
       </c>
       <c r="N277" t="inlineStr">
         <is>
@@ -27333,12 +27337,12 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -27377,10 +27381,10 @@
         </is>
       </c>
       <c r="L278" s="5" t="n">
-        <v>0.009214</v>
+        <v>0.002591</v>
       </c>
       <c r="M278" s="5" t="n">
-        <v>0.007263</v>
+        <v>0.002189</v>
       </c>
       <c r="N278" t="inlineStr">
         <is>
@@ -27411,12 +27415,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -27439,11 +27443,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I279" s="5" t="n">
-        <v>-0.008472</v>
-      </c>
-      <c r="J279" s="5" t="n">
-        <v>-0.002701</v>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -27451,10 +27459,10 @@
         </is>
       </c>
       <c r="L279" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.009214</v>
       </c>
       <c r="M279" s="5" t="n">
-        <v>-0.006417</v>
+        <v>0.007263</v>
       </c>
       <c r="N279" t="inlineStr">
         <is>
@@ -27485,10 +27493,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Advance royalty Note 19</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -27509,15 +27521,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I280" s="5" t="n">
+        <v>-0.008472</v>
+      </c>
+      <c r="J280" s="5" t="n">
+        <v>-0.002701</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -27525,10 +27533,10 @@
         </is>
       </c>
       <c r="L280" s="5" t="n">
-        <v>-0.031137</v>
+        <v>-0.0063</v>
       </c>
       <c r="M280" s="5" t="n">
-        <v>-0.06468500000000001</v>
+        <v>-0.006417</v>
       </c>
       <c r="N280" t="inlineStr">
         <is>
@@ -27559,7 +27567,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Share of loss of associate Note 19</t>
+          <t>Advance royalty Note 19</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -27599,10 +27607,10 @@
         </is>
       </c>
       <c r="L281" s="5" t="n">
-        <v>0.20124</v>
+        <v>-0.031137</v>
       </c>
       <c r="M281" s="5" t="n">
-        <v>0.186951</v>
+        <v>-0.06468500000000001</v>
       </c>
       <c r="N281" t="inlineStr">
         <is>
@@ -27633,14 +27641,10 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share of loss of associate Note 19</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -27677,10 +27681,10 @@
         </is>
       </c>
       <c r="L282" s="5" t="n">
-        <v>-3.064101</v>
+        <v>0.20124</v>
       </c>
       <c r="M282" s="5" t="n">
-        <v>-2.392547</v>
+        <v>0.186951</v>
       </c>
       <c r="N282" t="inlineStr">
         <is>
@@ -27706,15 +27710,19 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>not subsequently reclassify into income</t>
+          <t>Other (income) expense</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Exchange on translation of foreign subsidiaries</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -27751,10 +27759,10 @@
         </is>
       </c>
       <c r="L283" s="5" t="n">
-        <v>0.004424</v>
+        <v>-3.064101</v>
       </c>
       <c r="M283" s="5" t="n">
-        <v>0.007513</v>
+        <v>-2.392547</v>
       </c>
       <c r="N283" t="inlineStr">
         <is>
@@ -27785,14 +27793,10 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Net comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Exchange on translation of foreign subsidiaries</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -27829,10 +27833,10 @@
         </is>
       </c>
       <c r="L284" s="5" t="n">
-        <v>-3.068525</v>
+        <v>0.004424</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>-2.40006</v>
+        <v>0.007513</v>
       </c>
       <c r="N284" t="inlineStr">
         <is>
@@ -27858,15 +27862,19 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>shares       Amount       Stock Options       Warrants       Translation              Deficit           Total</t>
+          <t>not subsequently reclassify into income</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2020 (Note 3) 45,284,836 $ 6,480,295 $ 880,287 $ 774,775 $ (11,283) $</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
+          <t>Net comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -27903,10 +27911,10 @@
         </is>
       </c>
       <c r="L285" s="5" t="n">
-        <v>-0.21366</v>
+        <v>-3.068525</v>
       </c>
       <c r="M285" s="5" t="n">
-        <v>-8.337733999999999</v>
+        <v>-2.40006</v>
       </c>
       <c r="N285" t="inlineStr">
         <is>
@@ -27937,7 +27945,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Issued pursuant to private placement 20,000,000 5,000,000 - - -</t>
+          <t>Balance at December 31, 2020 (Note 3) 45,284,836 $ 6,480,295 $ 880,287 $ 774,775 $ (11,283) $</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -27977,12 +27985,10 @@
         </is>
       </c>
       <c r="L286" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.21366</v>
+      </c>
+      <c r="M286" s="5" t="n">
+        <v>-8.337733999999999</v>
       </c>
       <c r="N286" t="inlineStr">
         <is>
@@ -28013,7 +28019,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Warrants issued pursuant to private placement - (1,935,000) - 1,935,000 -</t>
+          <t>Issued pursuant to private placement 20,000,000 5,000,000 - - -</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -28052,10 +28058,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L287" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
@@ -28091,7 +28095,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Broker warrants issued pursuant to private placement - (12,000) - 12,000 -</t>
+          <t>Warrants issued pursuant to private placement - (1,935,000) - 1,935,000 -</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -28169,7 +28173,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Share issue costs - (75,807) - - -</t>
+          <t>Broker warrants issued pursuant to private placement - (12,000) - 12,000 -</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -28208,8 +28212,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L289" s="5" t="n">
-        <v>-0.075807</v>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
@@ -28245,7 +28251,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Expiry of stock options - - (202,243) - -</t>
+          <t>Share issue costs - (75,807) - - -</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -28284,13 +28290,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M290" s="5" t="n">
-        <v>0.202243</v>
+      <c r="L290" s="5" t="n">
+        <v>-0.075807</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N290" t="inlineStr">
         <is>
@@ -28321,7 +28327,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Expiry of warrants - - - (506,775) -</t>
+          <t>Expiry of stock options - - (202,243) - -</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -28366,7 +28372,7 @@
         </is>
       </c>
       <c r="M291" s="5" t="n">
-        <v>0.506775</v>
+        <v>0.202243</v>
       </c>
       <c r="N291" t="inlineStr">
         <is>
@@ -28397,7 +28403,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 500,000 - -</t>
+          <t>Expiry of warrants - - - (506,775) -</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -28436,13 +28442,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L292" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M292" s="5" t="n">
+        <v>0.506775</v>
       </c>
       <c r="N292" t="inlineStr">
         <is>
@@ -28473,14 +28479,10 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - -</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation - - 500,000 - -</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -28517,10 +28519,12 @@
         </is>
       </c>
       <c r="L293" s="5" t="n">
-        <v>-3.064101</v>
-      </c>
-      <c r="M293" s="5" t="n">
-        <v>-3.064101</v>
+        <v>0.5</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
@@ -28551,10 +28555,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Other comprehensive loss - - - - (4,424)</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>Net loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -28591,12 +28599,10 @@
         </is>
       </c>
       <c r="L294" s="5" t="n">
-        <v>-0.004424</v>
-      </c>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.064101</v>
+      </c>
+      <c r="M294" s="5" t="n">
+        <v>-3.064101</v>
       </c>
       <c r="N294" t="inlineStr">
         <is>
@@ -28627,7 +28633,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2021 (Note 3) 65,284,836 9,457,488 1,178,044 2,215,000 (15,707)</t>
+          <t>Other comprehensive loss - - - - (4,424)</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -28667,10 +28673,12 @@
         </is>
       </c>
       <c r="L295" s="5" t="n">
-        <v>2.142008</v>
-      </c>
-      <c r="M295" s="5" t="n">
-        <v>-10.692817</v>
+        <v>-0.004424</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
@@ -28701,7 +28709,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Expiry of stock options - - (101,333) - -</t>
+          <t>Balance at December 31, 2021 (Note 3) 65,284,836 9,457,488 1,178,044 2,215,000 (15,707)</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -28740,13 +28748,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L296" s="5" t="n">
+        <v>2.142008</v>
       </c>
       <c r="M296" s="5" t="n">
-        <v>0.101333</v>
+        <v>-10.692817</v>
       </c>
       <c r="N296" t="inlineStr">
         <is>
@@ -28777,7 +28783,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Expiry of warrants - - - (268,000) -</t>
+          <t>Expiry of stock options - - (101,333) - -</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -28822,7 +28828,7 @@
         </is>
       </c>
       <c r="M297" s="5" t="n">
-        <v>0.268</v>
+        <v>0.101333</v>
       </c>
       <c r="N297" t="inlineStr">
         <is>
@@ -28853,7 +28859,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 121,575 - -</t>
+          <t>Expiry of warrants - - - (268,000) -</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -28892,13 +28898,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L298" s="5" t="n">
-        <v>0.121575</v>
-      </c>
-      <c r="M298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M298" s="5" t="n">
+        <v>0.268</v>
       </c>
       <c r="N298" t="inlineStr">
         <is>
@@ -28929,7 +28935,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Other comprehensive loss - - - - (7,513)</t>
+          <t>Share-based compensation - - 121,575 - -</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -28969,7 +28975,7 @@
         </is>
       </c>
       <c r="L299" s="5" t="n">
-        <v>-0.007513</v>
+        <v>0.121575</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
@@ -29005,7 +29011,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2022 65,284,836 $ 9,457,488 $ 1,198,286 $ 1,947,000 $ (23,220) $</t>
+          <t>Other comprehensive loss - - - - (7,513)</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -29045,10 +29051,12 @@
         </is>
       </c>
       <c r="L300" s="5" t="n">
-        <v>-0.136477</v>
-      </c>
-      <c r="M300" s="5" t="n">
-        <v>-12.716031</v>
+        <v>-0.007513</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
@@ -29074,12 +29082,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>shares       Amount       Stock Options       Warrants       Translation              Deficit           Total</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 14)</t>
+          <t>Balance at December 31, 2022 65,284,836 $ 9,457,488 $ 1,198,286 $ 1,947,000 $ (23,220) $</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -29098,29 +29106,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H301" s="5" t="n">
-        <v>0.989795</v>
-      </c>
-      <c r="I301" s="5" t="n">
-        <v>1.999833</v>
-      </c>
-      <c r="J301" s="5" t="n">
-        <v>1.172084</v>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L301" s="5" t="n">
+        <v>-0.136477</v>
+      </c>
+      <c r="M301" s="5" t="n">
+        <v>-12.716031</v>
       </c>
       <c r="N301" t="inlineStr">
         <is>
@@ -29151,7 +29161,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Share based payments (Note 12)</t>
+          <t>Exploration and evaluation expenditures (Note 14)</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -29160,22 +29170,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F302" s="5" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="G302" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H302" s="5" t="n">
+        <v>0.989795</v>
       </c>
       <c r="I302" s="5" t="n">
-        <v>0.316</v>
+        <v>1.999833</v>
       </c>
       <c r="J302" s="5" t="n">
-        <v>0.269</v>
+        <v>1.172084</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
@@ -29221,33 +29233,29 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Salaries, director and management fees</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share based payments (Note 12)</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F303" s="5" t="n">
-        <v>0.196108</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G303" s="5" t="n">
-        <v>0.336191</v>
+        <v>0.02</v>
       </c>
       <c r="H303" s="5" t="n">
-        <v>0.336</v>
+        <v>0.176</v>
       </c>
       <c r="I303" s="5" t="n">
-        <v>0.326215</v>
+        <v>0.316</v>
       </c>
       <c r="J303" s="5" t="n">
-        <v>0.297382</v>
+        <v>0.269</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
@@ -29293,7 +29301,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Regulatory fees</t>
+          <t>Salaries, director and management fees</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -29307,19 +29315,19 @@
         </is>
       </c>
       <c r="F304" s="5" t="n">
-        <v>0.030008</v>
+        <v>0.196108</v>
       </c>
       <c r="G304" s="5" t="n">
-        <v>0.026279</v>
+        <v>0.336191</v>
       </c>
       <c r="H304" s="5" t="n">
-        <v>0.021944</v>
+        <v>0.336</v>
       </c>
       <c r="I304" s="5" t="n">
-        <v>0.026123</v>
+        <v>0.326215</v>
       </c>
       <c r="J304" s="5" t="n">
-        <v>0.023874</v>
+        <v>0.297382</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
@@ -29365,7 +29373,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Regulatory fees</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -29373,23 +29381,25 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E305" s="5" t="n">
-        <v>0.003705</v>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F305" s="5" t="n">
-        <v>0.008560999999999999</v>
+        <v>0.030008</v>
       </c>
       <c r="G305" s="5" t="n">
-        <v>0.01515</v>
+        <v>0.026279</v>
       </c>
       <c r="H305" s="5" t="n">
-        <v>0.01605</v>
+        <v>0.021944</v>
       </c>
       <c r="I305" s="5" t="n">
-        <v>0.018029</v>
+        <v>0.026123</v>
       </c>
       <c r="J305" s="5" t="n">
-        <v>0.018029</v>
+        <v>0.023874</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
@@ -29435,33 +29445,31 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E306" s="5" t="n">
-        <v>0.001705</v>
+        <v>0.003705</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>-0.000735</v>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.008560999999999999</v>
+      </c>
+      <c r="G306" s="5" t="n">
+        <v>0.01515</v>
       </c>
       <c r="H306" s="5" t="n">
-        <v>0.009051</v>
+        <v>0.01605</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>0.013701</v>
+        <v>0.018029</v>
       </c>
       <c r="J306" s="5" t="n">
-        <v>0.011122</v>
+        <v>0.018029</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -29502,42 +29510,36 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Other (income) expense</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Gain on disposition of property (Note 17)</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="n">
+        <v>0.001705</v>
+      </c>
+      <c r="F307" s="5" t="n">
+        <v>-0.000735</v>
+      </c>
+      <c r="G307" s="5" t="n">
+        <v>0.002301</v>
+      </c>
+      <c r="H307" s="5" t="n">
+        <v>0.009051</v>
+      </c>
+      <c r="I307" s="5" t="n">
+        <v>0.013701</v>
       </c>
       <c r="J307" s="5" t="n">
-        <v>-0.527</v>
+        <v>0.011122</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
@@ -29583,7 +29585,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Loss from investment in associate (Note 17)</t>
+          <t>Gain on disposition of property (Note 17)</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -29613,7 +29615,7 @@
         </is>
       </c>
       <c r="J308" s="5" t="n">
-        <v>0.047</v>
+        <v>-0.527</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
@@ -29659,14 +29661,10 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss from investment in associate (Note 17)</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -29687,11 +29685,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I309" s="5" t="n">
-        <v>-2.921476</v>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J309" s="5" t="n">
-        <v>-1.597942</v>
+        <v>0.047</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
@@ -29732,15 +29732,19 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>Other (income) expense</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Exchange on translation of foreign subsidiaries</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -29756,14 +29760,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H310" s="5" t="n">
-        <v>0.010455</v>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I310" s="5" t="n">
-        <v>0.000232</v>
+        <v>-2.921476</v>
       </c>
       <c r="J310" s="5" t="n">
-        <v>0.005658</v>
+        <v>-1.597942</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
@@ -29809,29 +29815,31 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Net comprehensive loss</t>
+          <t>Exchange on translation of foreign subsidiaries</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
-      <c r="E311" s="5" t="n">
-        <v>0.215405</v>
-      </c>
-      <c r="F311" s="5" t="n">
-        <v>0.68514</v>
-      </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G311" s="5" t="n">
+        <v>0.007125</v>
       </c>
       <c r="H311" s="5" t="n">
-        <v>1.705863</v>
+        <v>0.010455</v>
       </c>
       <c r="I311" s="5" t="n">
-        <v>2.921708</v>
+        <v>0.000232</v>
       </c>
       <c r="J311" s="5" t="n">
-        <v>1.6036</v>
+        <v>0.005658</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
@@ -29872,40 +29880,32 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>income</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Loss per share total</t>
+          <t>Net comprehensive loss</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E312" s="5" t="n">
+        <v>0.215405</v>
+      </c>
+      <c r="F312" s="5" t="n">
+        <v>0.68514</v>
+      </c>
+      <c r="G312" s="5" t="n">
+        <v>1.020579</v>
+      </c>
+      <c r="H312" s="5" t="n">
+        <v>1.705863</v>
       </c>
       <c r="I312" s="5" t="n">
-        <v>1e-07</v>
+        <v>2.921708</v>
       </c>
       <c r="J312" s="5" t="n">
-        <v>5e-08</v>
+        <v>1.6036</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
@@ -29946,12 +29946,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>- basic</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>- basic total</t>
+          <t>Loss per share total</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -30020,12 +30020,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>- basic</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding total</t>
+          <t>- basic total</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -30050,10 +30050,10 @@
         </is>
       </c>
       <c r="I314" s="5" t="n">
-        <v>28.761828</v>
+        <v>1e-07</v>
       </c>
       <c r="J314" s="5" t="n">
-        <v>35.259639</v>
+        <v>5e-08</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
@@ -30094,12 +30094,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>- basic</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>- basic</t>
+          <t>Weighted average number of common shares outstanding total</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -30127,7 +30127,7 @@
         <v>28.761828</v>
       </c>
       <c r="J315" s="5" t="n">
-        <v>0.259639</v>
+        <v>35.259639</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
@@ -30168,12 +30168,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>- basic</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Share based payments (Notes 10 and 12)</t>
+          <t>- basic</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -30192,16 +30192,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H316" s="5" t="n">
-        <v>0.176</v>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I316" s="5" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="J316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>28.761828</v>
+      </c>
+      <c r="J316" s="5" t="n">
+        <v>0.259639</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
@@ -30242,35 +30242,35 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Share based payments (Notes 10 and 12)</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F317" s="5" t="n">
-        <v>-0.007974</v>
-      </c>
-      <c r="G317" s="5" t="n">
-        <v>-0.00724</v>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H317" s="5" t="n">
-        <v>-0.005595</v>
+        <v>0.176</v>
       </c>
       <c r="I317" s="5" t="n">
-        <v>-0.008472</v>
+        <v>0.316</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
@@ -30321,28 +30321,30 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E318" s="5" t="n">
-        <v>-0.215405</v>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F318" s="5" t="n">
-        <v>-0.684316</v>
+        <v>-0.007974</v>
       </c>
       <c r="G318" s="5" t="n">
-        <v>-1.013454</v>
+        <v>-0.00724</v>
       </c>
       <c r="H318" s="5" t="n">
-        <v>-1.695408</v>
+        <v>-0.005595</v>
       </c>
       <c r="I318" s="5" t="n">
-        <v>-2.921476</v>
+        <v>-0.008472</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
@@ -30388,35 +30390,33 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E319" s="5" t="n">
-        <v>1e-08</v>
+        <v>-0.215405</v>
       </c>
       <c r="F319" s="5" t="n">
-        <v>5e-08</v>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.684316</v>
+      </c>
+      <c r="G319" s="5" t="n">
+        <v>-1.013454</v>
       </c>
       <c r="H319" s="5" t="n">
-        <v>7e-08</v>
+        <v>-1.695408</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>1e-07</v>
+        <v>-2.921476</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -30467,34 +30467,28 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Loss per share - basic and diluted</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E320" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="F320" s="5" t="n">
+        <v>5e-08</v>
+      </c>
+      <c r="G320" s="5" t="n">
+        <v>5.999999999999999e-08</v>
       </c>
       <c r="H320" s="5" t="n">
-        <v>22.574704</v>
+        <v>7e-08</v>
       </c>
       <c r="I320" s="5" t="n">
-        <v>28.761828</v>
+        <v>1e-07</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
@@ -30540,35 +30534,37 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>income</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 13)</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F321" s="5" t="n">
-        <v>0.218264</v>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G321" s="5" t="n">
-        <v>0.462306</v>
-      </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>17.765961</v>
+      </c>
+      <c r="H321" s="5" t="n">
+        <v>22.574704</v>
+      </c>
+      <c r="I321" s="5" t="n">
+        <v>28.761828</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
@@ -30619,29 +30615,23 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenditures (Note 13)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F322" s="5" t="n">
-        <v>-0.000735</v>
+        <v>0.218264</v>
       </c>
       <c r="G322" s="5" t="n">
-        <v>0.002301</v>
-      </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.462306</v>
+      </c>
+      <c r="H322" s="5" t="n">
+        <v>0.989795</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
@@ -30692,12 +30682,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>reclassify into income</t>
+          <t>income</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Exchange loss on translation of foreign subsidiary</t>
+          <t>Total 1,460,727 1,177,356 20,000 (1,013,454) (7,125) 1,637,504 176,000 (1,695,408)</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -30706,16 +30696,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F323" s="5" t="n">
-        <v>0.000824</v>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G323" s="5" t="n">
-        <v>0.007125</v>
-      </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.107641</v>
+      </c>
+      <c r="H323" s="5" t="n">
+        <v>-0.010455</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
@@ -30766,12 +30756,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>reclassify into income</t>
+          <t>of</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Net comprehensive loss</t>
+          <t>of part Amount 1,943,101 1,177,356</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -30780,16 +30770,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F324" s="5" t="n">
-        <v>0.68514</v>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G324" s="5" t="n">
-        <v>1.020579</v>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.120457</v>
+      </c>
+      <c r="H324" s="5" t="n">
+        <v>3.120457</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
@@ -30840,17 +30830,17 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>reclassify into income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted</t>
+          <t>Foreign exchange loss (gain)</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -30859,10 +30849,10 @@
         </is>
       </c>
       <c r="F325" s="5" t="n">
-        <v>5e-08</v>
+        <v>-0.000735</v>
       </c>
       <c r="G325" s="5" t="n">
-        <v>5.999999999999999e-08</v>
+        <v>0.002301</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -30923,24 +30913,20 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (Note 1)</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Exchange loss on translation of foreign subsidiary</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F326" s="5" t="n">
-        <v>14.574704</v>
+        <v>0.000824</v>
       </c>
       <c r="G326" s="5" t="n">
-        <v>17.765961</v>
+        <v>0.007125</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
@@ -30996,25 +30982,25 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>reclassify into income</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 12)</t>
+          <t>Net comprehensive loss</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
-      <c r="E327" s="5" t="n">
-        <v>0.11567</v>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F327" s="5" t="n">
-        <v>0.218264</v>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.68514</v>
+      </c>
+      <c r="G327" s="5" t="n">
+        <v>1.020579</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -31070,29 +31056,29 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>reclassify into income</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Salaries and management fees</t>
+          <t>Loss per share - basic and diluted</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E328" s="5" t="n">
-        <v>0.043981</v>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F328" s="5" t="n">
-        <v>0.196108</v>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5e-08</v>
+      </c>
+      <c r="G328" s="5" t="n">
+        <v>5.999999999999999e-08</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
@@ -31148,25 +31134,29 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>reclassify into income</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Share based payments (Note 11)</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" s="5" t="n">
-        <v>0.026111</v>
+          <t>Weighted average number of common shares outstanding (Note 1)</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F329" s="5" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14.574704</v>
+      </c>
+      <c r="G329" s="5" t="n">
+        <v>17.765961</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
@@ -31227,15 +31217,15 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Investor relations and regulatory</t>
+          <t>Exploration and evaluation expenditures (Note 12)</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" s="5" t="n">
-        <v>0.016345</v>
+        <v>0.11567</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>0.060559</v>
+        <v>0.218264</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
@@ -31296,22 +31286,24 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Exchange loss on translation of foreign subsidiary</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Salaries and management fees</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E331" s="5" t="n">
+        <v>0.043981</v>
       </c>
       <c r="F331" s="5" t="n">
-        <v>0.000824</v>
+        <v>0.196108</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
@@ -31372,71 +31364,295 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Share based payments (Note 11)</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" s="5" t="n">
+        <v>0.026111</v>
+      </c>
+      <c r="F332" s="5" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Investor relations and regulatory</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" s="5" t="n">
+        <v>0.016345</v>
+      </c>
+      <c r="F333" s="5" t="n">
+        <v>0.060559</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
           <t>income</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr">
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Exchange loss on translation of foreign subsidiary</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F334" s="5" t="n">
+        <v>0.000824</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>income</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
         <is>
           <t>Weighted average number of common shares outstanding (Note 1)</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr">
+      <c r="D335" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E332" s="5" t="n">
+      <c r="E335" s="5" t="n">
         <v>14.574704</v>
       </c>
-      <c r="F332" s="5" t="n">
+      <c r="F335" s="5" t="n">
         <v>14.574704</v>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P332" t="inlineStr">
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
         <is>
           <t>-</t>
         </is>
